--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3185"/>
+  <dimension ref="A1:E3186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86411,6 +86411,33 @@
         </is>
       </c>
     </row>
+    <row r="3186">
+      <c r="A3186" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B3186" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3186" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3186" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3186" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3186"/>
+  <dimension ref="A1:E3187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86438,6 +86438,33 @@
         </is>
       </c>
     </row>
+    <row r="3187">
+      <c r="A3187" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3187" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3187" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3187" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3349"/>
+  <dimension ref="A1:E3350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90839,6 +90839,33 @@
         </is>
       </c>
     </row>
+    <row r="3350">
+      <c r="A3350" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3350" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3350" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3350" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3350" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3350"/>
+  <dimension ref="A1:E3351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90866,6 +90866,33 @@
         </is>
       </c>
     </row>
+    <row r="3351">
+      <c r="A3351" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B3351" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3351" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D3351" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3351" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3451"/>
+  <dimension ref="A1:E3452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -93602,6 +93590,33 @@
       <c r="E3451" t="inlineStr">
         <is>
           <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B3452" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3452" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D3452" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3452" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3452"/>
+  <dimension ref="A1:E3453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93620,6 +93620,33 @@
         </is>
       </c>
     </row>
+    <row r="3453">
+      <c r="A3453" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B3453" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3453" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D3453" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3453" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
